--- a/docs/StructureDefinition-Organization-twltc.xlsx
+++ b/docs/StructureDefinition-Organization-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization-twltc.xlsx
+++ b/docs/StructureDefinition-Organization-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization-twltc.xlsx
+++ b/docs/StructureDefinition-Organization-twltc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization-twltc.xlsx
+++ b/docs/StructureDefinition-Organization-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization-twltc.xlsx
+++ b/docs/StructureDefinition-Organization-twltc.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3576" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3574" uniqueCount="625">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -596,14 +596,7 @@
     <t>Identifier.type</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>CX.5</t>
   </si>
   <si>
     <t>Organization.identifier.system</t>
@@ -774,6 +767,15 @@
     <t>http://hl7.org/fhir/ValueSet/organization-type</t>
   </si>
   <si>
+    <t>No equivalent in v2</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
     <t>Organization.name</t>
   </si>
   <si>
@@ -991,17 +993,21 @@
     <t>為了聯絡、計費或通報要求而可能需要追踪機構的地址</t>
   </si>
   <si>
+    <t xml:space="preserve">org-2
+</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
-    <t>XAD</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>Address</t>
+    <t>ORC-23?</t>
+  </si>
+  <si>
+    <t>.address</t>
+  </si>
+  <si>
+    <t>./PrimaryAddress and ./OtherAddresses</t>
   </si>
   <si>
     <t>Organization.address.id</t>
@@ -1395,6 +1401,10 @@
     <t>臺灣郵遞區號</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Organization.address.postalCode.extension:PostalCode.id</t>
   </si>
   <si>
@@ -1496,10 +1506,10 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
   </si>
   <si>
     <t>Organization.address.postalCode.extension:PostalCode.value[x].coding:PostalCode3</t>
@@ -1867,9 +1877,6 @@
     <t>表明可聯絡到此聯絡人的聯絡方式之用途</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>需要對多個聯絡人進行區分</t>
   </si>
   <si>
@@ -1877,6 +1884,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+  </si>
+  <si>
+    <t>./type</t>
   </si>
   <si>
     <t>Organization.contact.name</t>
@@ -1925,13 +1935,16 @@
     <t>可到訪及郵寄聯絡人的地址</t>
   </si>
   <si>
-    <t>注意：地址的目的是描述用於管理目的之郵政地址，而不是描述絕對的地理座標。郵政地址經常被用作實體位置的代表（亦可見[Location](http://hl7.org/fhir/R4/location.html#)resource）。</t>
+    <t>PID-11</t>
+  </si>
+  <si>
+    <t>./addr</t>
   </si>
   <si>
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -3924,7 +3937,7 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
         <v>177</v>
@@ -3997,16 +4010,16 @@
         <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>20</v>
@@ -4017,10 +4030,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4046,16 +4059,16 @@
         <v>100</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -4068,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>20</v>
@@ -4104,7 +4117,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -4119,13 +4132,13 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>20</v>
@@ -4133,10 +4146,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4162,13 +4175,13 @@
         <v>155</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4182,7 +4195,7 @@
         <v>20</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>20</v>
@@ -4218,7 +4231,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -4233,13 +4246,13 @@
         <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>20</v>
@@ -4247,10 +4260,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4273,13 +4286,13 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4330,7 +4343,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -4345,13 +4358,13 @@
         <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>20</v>
@@ -4359,10 +4372,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4385,16 +4398,16 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4444,7 +4457,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4459,13 +4472,13 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>20</v>
@@ -4473,10 +4486,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4499,26 +4512,26 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N20" t="s" s="2">
+      <c r="P20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q20" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="O20" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="P20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q20" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="R20" t="s" s="2">
         <v>20</v>
       </c>
@@ -4562,7 +4575,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4577,24 +4590,24 @@
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>234</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4614,22 +4627,22 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
         <v>177</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4654,14 +4667,14 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="Z21" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="Y21" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>242</v>
-      </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
       </c>
@@ -4678,7 +4691,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4687,30 +4700,30 @@
         <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>187</v>
+        <v>241</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4736,16 +4749,16 @@
         <v>155</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4794,7 +4807,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4809,13 +4822,13 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
@@ -4823,10 +4836,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4852,16 +4865,16 @@
         <v>155</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4910,7 +4923,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4928,7 +4941,7 @@
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
@@ -4939,10 +4952,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4965,19 +4978,19 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -5026,7 +5039,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -5035,19 +5048,19 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
@@ -5055,10 +5068,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5167,10 +5180,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5199,7 +5212,7 @@
         <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5279,10 +5292,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5308,10 +5321,10 @@
         <v>106</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5341,10 +5354,10 @@
         <v>171</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -5362,7 +5375,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -5371,19 +5384,19 @@
         <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>20</v>
@@ -5391,10 +5404,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5420,16 +5433,16 @@
         <v>155</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5478,7 +5491,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5493,13 +5506,13 @@
         <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>20</v>
@@ -5507,10 +5520,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5536,16 +5549,16 @@
         <v>106</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5573,10 +5586,10 @@
         <v>171</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5594,7 +5607,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5609,13 +5622,13 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>20</v>
@@ -5623,10 +5636,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5649,16 +5662,16 @@
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5708,7 +5721,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5737,10 +5750,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5763,13 +5776,13 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5820,7 +5833,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5838,10 +5851,10 @@
         <v>130</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>20</v>
@@ -5849,10 +5862,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5875,19 +5888,19 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5936,7 +5949,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5945,19 +5958,19 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>186</v>
+        <v>314</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
@@ -5965,10 +5978,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6077,10 +6090,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6109,7 +6122,7 @@
         <v>134</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>136</v>
@@ -6191,13 +6204,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="B35" t="s" s="2">
-        <v>318</v>
-      </c>
       <c r="C35" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>20</v>
@@ -6219,13 +6232,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6305,13 +6318,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>20</v>
@@ -6333,13 +6346,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6419,13 +6432,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>20</v>
@@ -6447,13 +6460,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6533,13 +6546,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>20</v>
@@ -6561,13 +6574,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6647,16 +6660,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6675,13 +6688,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6761,13 +6774,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>20</v>
@@ -6789,13 +6802,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6875,13 +6888,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>20</v>
@@ -6903,13 +6916,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6989,16 +7002,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7017,13 +7030,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7103,10 +7116,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7132,16 +7145,16 @@
         <v>106</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7154,7 +7167,7 @@
         <v>20</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>20</v>
@@ -7169,10 +7182,10 @@
         <v>171</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -7190,7 +7203,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -7205,13 +7218,13 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -7219,10 +7232,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7248,13 +7261,13 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7268,7 +7281,7 @@
         <v>20</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>20</v>
@@ -7283,10 +7296,10 @@
         <v>171</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -7304,7 +7317,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -7319,10 +7332,10 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>20</v>
@@ -7333,10 +7346,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7362,16 +7375,16 @@
         <v>155</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7384,7 +7397,7 @@
         <v>20</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>20</v>
@@ -7420,7 +7433,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7435,10 +7448,10 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>20</v>
@@ -7449,14 +7462,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7478,10 +7491,10 @@
         <v>155</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7496,7 +7509,7 @@
         <v>20</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>20</v>
@@ -7532,7 +7545,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7547,13 +7560,13 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7561,14 +7574,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7590,10 +7603,10 @@
         <v>155</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7608,7 +7621,7 @@
         <v>20</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>20</v>
@@ -7644,7 +7657,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7659,13 +7672,13 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
@@ -7673,14 +7686,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7702,13 +7715,13 @@
         <v>155</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7722,7 +7735,7 @@
         <v>20</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>20</v>
@@ -7758,7 +7771,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7773,10 +7786,10 @@
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
@@ -7787,14 +7800,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7816,10 +7829,10 @@
         <v>155</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7870,7 +7883,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7885,13 +7898,13 @@
         <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
@@ -7899,14 +7912,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7928,10 +7941,10 @@
         <v>155</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7946,7 +7959,7 @@
         <v>20</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>20</v>
@@ -7982,7 +7995,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7997,13 +8010,13 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>20</v>
@@ -8011,10 +8024,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8040,7 +8053,7 @@
         <v>155</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M51" t="s" s="2">
         <v>157</v>
@@ -8123,10 +8136,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8233,13 +8246,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>20</v>
@@ -8261,13 +8274,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8327,7 +8340,7 @@
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>186</v>
+        <v>444</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>138</v>
@@ -8347,10 +8360,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8459,10 +8472,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8488,10 +8501,10 @@
         <v>133</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8571,10 +8584,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8600,13 +8613,13 @@
         <v>100</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8614,7 +8627,7 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>20</v>
@@ -8656,7 +8669,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>86</v>
@@ -8685,10 +8698,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8714,13 +8727,13 @@
         <v>177</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8770,7 +8783,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8779,16 +8792,16 @@
         <v>86</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>188</v>
+        <v>130</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>20</v>
@@ -8799,10 +8812,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8911,10 +8924,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8940,13 +8953,13 @@
         <v>133</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9025,10 +9038,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9048,22 +9061,22 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9100,7 +9113,7 @@
         <v>20</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
@@ -9110,7 +9123,7 @@
         <v>164</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -9119,16 +9132,16 @@
         <v>78</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>20</v>
@@ -9139,13 +9152,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>20</v>
@@ -9164,22 +9177,22 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9207,10 +9220,10 @@
         <v>171</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -9228,7 +9241,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -9237,16 +9250,16 @@
         <v>78</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>20</v>
@@ -9257,10 +9270,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9369,10 +9382,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9401,10 +9414,10 @@
         <v>161</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9483,10 +9496,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9512,16 +9525,16 @@
         <v>100</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9531,7 +9544,7 @@
         <v>20</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>20</v>
@@ -9570,7 +9583,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9585,10 +9598,10 @@
         <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>20</v>
@@ -9599,10 +9612,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9628,13 +9641,13 @@
         <v>155</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9684,7 +9697,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9699,10 +9712,10 @@
         <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>20</v>
@@ -9713,10 +9726,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9742,14 +9755,14 @@
         <v>106</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9798,7 +9811,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9813,10 +9826,10 @@
         <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
@@ -9827,10 +9840,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9856,14 +9869,14 @@
         <v>155</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -9912,7 +9925,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9927,10 +9940,10 @@
         <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
@@ -9941,10 +9954,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9967,19 +9980,19 @@
         <v>87</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10028,7 +10041,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -10043,10 +10056,10 @@
         <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
@@ -10057,13 +10070,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>20</v>
@@ -10082,22 +10095,22 @@
         <v>20</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10125,10 +10138,10 @@
         <v>171</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -10146,7 +10159,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -10155,16 +10168,16 @@
         <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>20</v>
@@ -10175,10 +10188,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10287,10 +10300,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10319,10 +10332,10 @@
         <v>161</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10401,10 +10414,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10430,16 +10443,16 @@
         <v>100</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -10449,7 +10462,7 @@
         <v>20</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>20</v>
@@ -10488,7 +10501,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10503,10 +10516,10 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>20</v>
@@ -10517,10 +10530,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10546,13 +10559,13 @@
         <v>155</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10602,7 +10615,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10617,10 +10630,10 @@
         <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>20</v>
@@ -10631,10 +10644,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10660,14 +10673,14 @@
         <v>106</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -10716,7 +10729,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10731,10 +10744,10 @@
         <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>20</v>
@@ -10745,10 +10758,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10774,14 +10787,14 @@
         <v>155</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -10830,7 +10843,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10845,10 +10858,10 @@
         <v>98</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>20</v>
@@ -10859,10 +10872,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10885,19 +10898,19 @@
         <v>87</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -10946,7 +10959,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10961,10 +10974,10 @@
         <v>98</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>20</v>
@@ -10975,13 +10988,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>20</v>
@@ -11000,22 +11013,22 @@
         <v>20</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -11043,10 +11056,10 @@
         <v>171</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>20</v>
@@ -11064,7 +11077,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -11073,16 +11086,16 @@
         <v>78</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>20</v>
@@ -11093,10 +11106,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11205,10 +11218,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11237,10 +11250,10 @@
         <v>161</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11319,10 +11332,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11348,16 +11361,16 @@
         <v>100</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11367,7 +11380,7 @@
         <v>20</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>20</v>
@@ -11406,7 +11419,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11421,10 +11434,10 @@
         <v>98</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>20</v>
@@ -11435,10 +11448,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11464,13 +11477,13 @@
         <v>155</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11520,7 +11533,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -11535,10 +11548,10 @@
         <v>98</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>20</v>
@@ -11549,10 +11562,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11578,14 +11591,14 @@
         <v>106</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -11634,7 +11647,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11649,10 +11662,10 @@
         <v>98</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>20</v>
@@ -11663,10 +11676,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11692,14 +11705,14 @@
         <v>155</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -11748,7 +11761,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11763,10 +11776,10 @@
         <v>98</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>20</v>
@@ -11777,10 +11790,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11803,19 +11816,19 @@
         <v>87</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -11864,7 +11877,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -11879,10 +11892,10 @@
         <v>98</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>20</v>
@@ -11893,10 +11906,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11922,16 +11935,16 @@
         <v>155</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>20</v>
@@ -11980,7 +11993,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -11995,10 +12008,10 @@
         <v>98</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>20</v>
@@ -12009,10 +12022,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12038,10 +12051,10 @@
         <v>155</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12065,7 +12078,7 @@
         <v>20</v>
       </c>
       <c r="W86" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="X86" t="s" s="2">
         <v>20</v>
@@ -12092,7 +12105,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -12121,10 +12134,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12150,13 +12163,13 @@
         <v>155</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12206,7 +12219,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -12221,13 +12234,13 @@
         <v>98</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>20</v>
@@ -12235,10 +12248,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12261,17 +12274,17 @@
         <v>87</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12284,7 +12297,7 @@
         <v>20</v>
       </c>
       <c r="T88" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="U88" t="s" s="2">
         <v>20</v>
@@ -12320,7 +12333,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -12335,13 +12348,13 @@
         <v>98</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>20</v>
@@ -12349,10 +12362,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12375,17 +12388,17 @@
         <v>87</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -12434,7 +12447,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12449,10 +12462,10 @@
         <v>98</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>159</v>
@@ -12463,10 +12476,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12489,19 +12502,19 @@
         <v>20</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -12550,7 +12563,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -12568,7 +12581,7 @@
         <v>20</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>20</v>
@@ -12579,10 +12592,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12691,10 +12704,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12723,10 +12736,10 @@
         <v>161</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12805,10 +12818,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12834,16 +12847,16 @@
         <v>133</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>20</v>
@@ -12892,7 +12905,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -12921,10 +12934,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12950,16 +12963,14 @@
         <v>177</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -12987,10 +12998,10 @@
         <v>182</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>20</v>
@@ -13008,7 +13019,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -13017,16 +13028,16 @@
         <v>86</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>188</v>
+        <v>603</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>20</v>
@@ -13037,10 +13048,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13063,17 +13074,17 @@
         <v>20</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -13122,7 +13133,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -13137,10 +13148,10 @@
         <v>98</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>20</v>
@@ -13151,10 +13162,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13177,17 +13188,17 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -13236,7 +13247,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -13251,10 +13262,10 @@
         <v>98</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>20</v>
@@ -13265,10 +13276,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13291,19 +13302,17 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -13352,7 +13361,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
@@ -13361,19 +13370,19 @@
         <v>86</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>314</v>
+        <v>619</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>315</v>
+        <v>620</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>316</v>
+        <v>20</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>20</v>
@@ -13381,10 +13390,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13407,17 +13416,17 @@
         <v>20</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>20</v>
@@ -13466,7 +13475,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>

--- a/docs/StructureDefinition-Organization-twltc.xlsx
+++ b/docs/StructureDefinition-Organization-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization-twltc.xlsx
+++ b/docs/StructureDefinition-Organization-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
